--- a/experiment/test/results-Set14/Set14.xlsx
+++ b/experiment/test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.07</v>
+        <v>24.15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5405</v>
+        <v>0.6455</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.87</v>
+        <v>27.32</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7544</v>
+        <v>0.8163</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.41</v>
+        <v>26.87</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6388</v>
+        <v>0.7403999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.29</v>
+        <v>27.56</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5794</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.7</v>
+        <v>25.75</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7466</v>
+        <v>0.8419</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.96</v>
+        <v>34.1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7967</v>
+        <v>0.8358</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.51</v>
+        <v>30.7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8265</v>
+        <v>0.8861</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.08</v>
+        <v>35.23</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9238</v>
+        <v>0.9458</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.64</v>
+        <v>34.41</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8676</v>
+        <v>0.8963</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.4</v>
+        <v>28.93</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7519</v>
+        <v>0.8179</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33.54</v>
+        <v>35.97</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9483</v>
+        <v>0.9656</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.37</v>
+        <v>35.62</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8815</v>
+        <v>0.8995</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.84</v>
+        <v>28.45</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9539</v>
+        <v>0.9688</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.77</v>
+        <v>30.29</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7837</v>
+        <v>0.8638</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.75</v>
+        <v>30.38</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7853</v>
+        <v>0.8433</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/test/results-Set14/Set14.xlsx
+++ b/experiment/test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.15</v>
+        <v>22.66</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6455</v>
+        <v>0.4955</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.32</v>
+        <v>25.58</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8163</v>
+        <v>0.7171999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.87</v>
+        <v>24.87</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.6088</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.56</v>
+        <v>25.75</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.5527</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.75</v>
+        <v>22.22</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8419</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.1</v>
+        <v>32.07</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8358</v>
+        <v>0.7727000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.7</v>
+        <v>26.21</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8861</v>
+        <v>0.7547</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.23</v>
+        <v>29.99</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9458</v>
+        <v>0.8588</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34.41</v>
+        <v>30.62</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8963</v>
+        <v>0.8331</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28.93</v>
+        <v>26.24</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8179</v>
+        <v>0.7072000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35.97</v>
+        <v>28.36</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9656</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.62</v>
+        <v>31.43</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8995</v>
+        <v>0.8427</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28.45</v>
+        <v>22.68</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9688</v>
+        <v>0.8393</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30.29</v>
+        <v>25.2</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8638</v>
+        <v>0.7339</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30.38</v>
+        <v>26.71</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8433</v>
+        <v>0.732</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/test/results-Set14/Set14.xlsx
+++ b/experiment/test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.07</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5376</v>
+        <v>0.5338000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.35</v>
+        <v>26.01</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7628</v>
+        <v>0.7536</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.44</v>
+        <v>25.43</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6397</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.36</v>
+        <v>26.35</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5821</v>
+        <v>0.5777</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.63</v>
+        <v>23.55</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7382</v>
+        <v>0.7355</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.97</v>
+        <v>32.89</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7965</v>
+        <v>0.7948</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.41</v>
+        <v>28.32</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8225</v>
+        <v>0.8207</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.08</v>
+        <v>33.86</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9242</v>
+        <v>0.9227</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.57</v>
+        <v>32.53</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8658</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.4</v>
+        <v>27.37</v>
       </c>
       <c r="C11" t="n">
-        <v>0.751</v>
+        <v>0.7498</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33.2</v>
+        <v>32.98</v>
       </c>
       <c r="C12" t="n">
-        <v>0.946</v>
+        <v>0.9452</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.26</v>
+        <v>34.19</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8806</v>
+        <v>0.8796</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.74</v>
+        <v>26.4</v>
       </c>
       <c r="C14" t="n">
-        <v>0.948</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.51</v>
+        <v>27.24</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7799</v>
+        <v>0.7771</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.71</v>
+        <v>28.58</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7839</v>
+        <v>0.7814</v>
       </c>
     </row>
   </sheetData>
